--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:06:57+00:00</t>
+    <t>2026-05-08T09:33:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:33:11+00:00</t>
+    <t>2026-05-08T10:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:00:47+00:00</t>
+    <t>2026-05-08T10:09:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:09:24+00:00</t>
+    <t>2026-05-08T11:19:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T11:19:22+00:00</t>
+    <t>2026-05-08T15:55:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T15:55:34+00:00</t>
+    <t>2026-06-26T06:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsTestValueSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T06:37:03+00:00</t>
+    <t>2026-06-26T06:47:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
